--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.120.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.120.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.120.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.120.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: hot to be allowed in taxation of costsâ€”Provided never-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]113</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]113</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L44: symbol-only separator/garbage line :: (136).</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L6: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]113</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: H</t>
+          <t>L6: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -720,7 +724,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: /</t>
+          <t>L63: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -765,7 +769,11 @@
           <t>L110: symbol-only separator/garbage line :: (138).</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L85: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -805,7 +813,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -1005,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1044,7 +1052,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
